--- a/docs/exports/metrics_full.xlsx
+++ b/docs/exports/metrics_full.xlsx
@@ -475,22 +475,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>197771</v>
+        <v>197728</v>
       </c>
       <c r="C2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="E2" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="F2" t="n">
-        <v>1145</v>
+        <v>1127</v>
       </c>
       <c r="G2" t="n">
-        <v>10.4</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="3">
@@ -500,22 +500,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80819</v>
+        <v>79331</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="D3" t="n">
-        <v>-3.7</v>
+        <v>-5.9</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="F3" t="n">
-        <v>1159</v>
+        <v>1125</v>
       </c>
       <c r="G3" t="n">
-        <v>6.3</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="4">
@@ -525,14 +525,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>159186</v>
+        <v>159044</v>
       </c>
       <c r="C4" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>1260</v>
+      </c>
       <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -542,22 +544,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>120910</v>
+        <v>121001</v>
       </c>
       <c r="C5" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="E5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="F5" t="n">
-        <v>1093</v>
+        <v>1066</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="6">
@@ -567,22 +569,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>162500</v>
+        <v>161635</v>
       </c>
       <c r="C6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="E6" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="F6" t="n">
-        <v>1000</v>
+        <v>991</v>
       </c>
       <c r="G6" t="n">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="7">
@@ -592,22 +594,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>207100</v>
+        <v>205439</v>
       </c>
       <c r="C7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4</v>
+        <v>1.2</v>
       </c>
       <c r="E7" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="F7" t="n">
-        <v>1159</v>
+        <v>1192</v>
       </c>
       <c r="G7" t="n">
-        <v>4.7</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="8">
@@ -617,22 +619,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>183529</v>
+        <v>181401</v>
       </c>
       <c r="C8" t="n">
         <v>3.5</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="E8" t="n">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="F8" t="n">
-        <v>1281</v>
+        <v>1300</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -642,10 +644,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>94087</v>
+        <v>97180</v>
       </c>
       <c r="C9" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -659,15 +661,15 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>211379</v>
+        <v>208269</v>
       </c>
       <c r="C10" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>991</v>
+        <v>1030</v>
       </c>
       <c r="G10" t="inlineStr"/>
     </row>
@@ -729,22 +731,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>745362</v>
+        <v>740473</v>
       </c>
       <c r="C2" t="n">
-        <v>6.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>-22.9</v>
+        <v>-24.3</v>
       </c>
       <c r="E2" t="n">
-        <v>16.8</v>
+        <v>16.3</v>
       </c>
       <c r="F2" t="n">
-        <v>3702</v>
+        <v>3778</v>
       </c>
       <c r="G2" t="n">
-        <v>21.2</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="3">
@@ -754,22 +756,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>823531</v>
+        <v>823085</v>
       </c>
       <c r="C3" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="D3" t="n">
-        <v>-29.1</v>
+        <v>-30</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>15.4</v>
       </c>
       <c r="F3" t="n">
-        <v>4287</v>
+        <v>4446</v>
       </c>
       <c r="G3" t="n">
-        <v>25.8</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="4">
@@ -779,19 +781,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1127243</v>
+        <v>1126984</v>
       </c>
       <c r="C4" t="n">
-        <v>7.2</v>
+        <v>9.5</v>
       </c>
       <c r="D4" t="n">
-        <v>-26.8</v>
+        <v>-27.3</v>
       </c>
       <c r="E4" t="n">
-        <v>16.3</v>
+        <v>15.8</v>
       </c>
       <c r="F4" t="n">
-        <v>5758</v>
+        <v>5958</v>
       </c>
       <c r="G4" t="n">
         <v>27.5</v>
@@ -804,22 +806,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1040849</v>
+        <v>1042419</v>
       </c>
       <c r="C5" t="n">
-        <v>8.4</v>
+        <v>10.4</v>
       </c>
       <c r="D5" t="n">
-        <v>-26.9</v>
+        <v>-28.1</v>
       </c>
       <c r="E5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="F5" t="n">
-        <v>4781</v>
+        <v>5001</v>
       </c>
       <c r="G5" t="n">
-        <v>25.1</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="6">
@@ -829,22 +831,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1045061</v>
+        <v>1059563</v>
       </c>
       <c r="C6" t="n">
-        <v>12.6</v>
+        <v>14.6</v>
       </c>
       <c r="D6" t="n">
-        <v>-20.5</v>
+        <v>-23.1</v>
       </c>
       <c r="E6" t="n">
-        <v>23.7</v>
+        <v>24.6</v>
       </c>
       <c r="F6" t="n">
-        <v>3677</v>
+        <v>3592</v>
       </c>
       <c r="G6" t="n">
-        <v>25.1</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="7">
@@ -854,22 +856,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1065276</v>
+        <v>1068686</v>
       </c>
       <c r="C7" t="n">
-        <v>8.199999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="D7" t="n">
-        <v>-23.1</v>
+        <v>-24.2</v>
       </c>
       <c r="E7" t="n">
-        <v>23.3</v>
+        <v>22.4</v>
       </c>
       <c r="F7" t="n">
-        <v>3811</v>
+        <v>3972</v>
       </c>
       <c r="G7" t="n">
-        <v>25.4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -879,22 +881,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1413716</v>
+        <v>1428555</v>
       </c>
       <c r="C8" t="n">
-        <v>12.6</v>
+        <v>14.9</v>
       </c>
       <c r="D8" t="n">
-        <v>-17</v>
+        <v>-18.2</v>
       </c>
       <c r="E8" t="n">
-        <v>26.6</v>
+        <v>25.9</v>
       </c>
       <c r="F8" t="n">
-        <v>4428</v>
+        <v>4590</v>
       </c>
       <c r="G8" t="n">
-        <v>22.8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -904,22 +906,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1165294</v>
+        <v>1171546</v>
       </c>
       <c r="C9" t="n">
-        <v>8.199999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="D9" t="n">
-        <v>-9.1</v>
+        <v>-8.1</v>
       </c>
       <c r="E9" t="n">
-        <v>29.2</v>
+        <v>26.3</v>
       </c>
       <c r="F9" t="n">
-        <v>3321</v>
+        <v>3715</v>
       </c>
       <c r="G9" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
@@ -929,22 +931,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1997982</v>
+        <v>2015424</v>
       </c>
       <c r="C10" t="n">
-        <v>17.3</v>
+        <v>19.5</v>
       </c>
       <c r="D10" t="n">
-        <v>-13.1</v>
+        <v>-14.5</v>
       </c>
       <c r="E10" t="n">
-        <v>28.6</v>
+        <v>28.3</v>
       </c>
       <c r="F10" t="n">
-        <v>5815</v>
+        <v>5942</v>
       </c>
       <c r="G10" t="n">
-        <v>25.5</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="11">
@@ -954,22 +956,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1529903</v>
+        <v>1545349</v>
       </c>
       <c r="C11" t="n">
-        <v>14.7</v>
+        <v>17.1</v>
       </c>
       <c r="D11" t="n">
-        <v>-18.9</v>
+        <v>-20.1</v>
       </c>
       <c r="E11" t="n">
-        <v>27.4</v>
+        <v>28</v>
       </c>
       <c r="F11" t="n">
-        <v>4646</v>
+        <v>4605</v>
       </c>
       <c r="G11" t="n">
-        <v>24.9</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="12">
@@ -979,22 +981,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1623833</v>
+        <v>1620022</v>
       </c>
       <c r="C12" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.8</v>
+        <v>-16.1</v>
       </c>
       <c r="E12" t="n">
-        <v>31.5</v>
+        <v>29.7</v>
       </c>
       <c r="F12" t="n">
-        <v>4299</v>
+        <v>4540</v>
       </c>
       <c r="G12" t="n">
-        <v>22.2</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="13">
@@ -1004,22 +1006,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1668808</v>
+        <v>1685324</v>
       </c>
       <c r="C13" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="D13" t="n">
-        <v>-18.3</v>
+        <v>-20.7</v>
       </c>
       <c r="E13" t="n">
-        <v>29.1</v>
+        <v>27.8</v>
       </c>
       <c r="F13" t="n">
-        <v>4779</v>
+        <v>5058</v>
       </c>
       <c r="G13" t="n">
-        <v>23.8</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="14">
@@ -1029,22 +1031,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2240162</v>
+        <v>2261580</v>
       </c>
       <c r="C14" t="n">
-        <v>15.4</v>
+        <v>18.8</v>
       </c>
       <c r="D14" t="n">
-        <v>-12.2</v>
+        <v>-13.8</v>
       </c>
       <c r="E14" t="n">
-        <v>44</v>
+        <v>42.4</v>
       </c>
       <c r="F14" t="n">
-        <v>4247</v>
+        <v>4440</v>
       </c>
       <c r="G14" t="n">
-        <v>18</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="15">
@@ -1054,22 +1056,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1820717</v>
+        <v>1833048</v>
       </c>
       <c r="C15" t="n">
-        <v>14.5</v>
+        <v>17.6</v>
       </c>
       <c r="D15" t="n">
-        <v>-11.7</v>
+        <v>-15.1</v>
       </c>
       <c r="E15" t="n">
-        <v>37.8</v>
+        <v>36.7</v>
       </c>
       <c r="F15" t="n">
-        <v>4010</v>
+        <v>4159</v>
       </c>
       <c r="G15" t="n">
-        <v>18.6</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="16">
@@ -1079,22 +1081,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1701483</v>
+        <v>1717942</v>
       </c>
       <c r="C16" t="n">
-        <v>11.4</v>
+        <v>14.1</v>
       </c>
       <c r="D16" t="n">
-        <v>-14.7</v>
+        <v>-15.7</v>
       </c>
       <c r="E16" t="n">
-        <v>37</v>
+        <v>35.3</v>
       </c>
       <c r="F16" t="n">
-        <v>3828</v>
+        <v>4050</v>
       </c>
       <c r="G16" t="n">
-        <v>22.1</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="17">
@@ -1104,22 +1106,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2490120</v>
+        <v>2505204</v>
       </c>
       <c r="C17" t="n">
-        <v>16.3</v>
+        <v>18.9</v>
       </c>
       <c r="D17" t="n">
-        <v>-16.6</v>
+        <v>-18.4</v>
       </c>
       <c r="E17" t="n">
-        <v>41.1</v>
+        <v>39.9</v>
       </c>
       <c r="F17" t="n">
-        <v>5052</v>
+        <v>5228</v>
       </c>
       <c r="G17" t="n">
-        <v>26.9</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="18">
@@ -1129,15 +1131,15 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>930768</v>
+        <v>947522</v>
       </c>
       <c r="C18" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>4013</v>
+        <v>4062</v>
       </c>
       <c r="G18" t="inlineStr"/>
     </row>
@@ -1148,15 +1150,15 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2010403</v>
+        <v>2007754</v>
       </c>
       <c r="C19" t="n">
-        <v>14.8</v>
+        <v>16.7</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>5577</v>
+        <v>6200</v>
       </c>
       <c r="G19" t="inlineStr"/>
     </row>
@@ -1167,22 +1169,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1747653</v>
+        <v>1761605</v>
       </c>
       <c r="C20" t="n">
-        <v>16</v>
+        <v>18.6</v>
       </c>
       <c r="D20" t="n">
-        <v>-18.4</v>
+        <v>-17.7</v>
       </c>
       <c r="E20" t="n">
-        <v>32</v>
+        <v>30.6</v>
       </c>
       <c r="F20" t="n">
-        <v>4551</v>
+        <v>4792</v>
       </c>
       <c r="G20" t="n">
-        <v>27.2</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="21">
@@ -1192,15 +1194,15 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1373148</v>
+        <v>1380387</v>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>3347</v>
+        <v>3260</v>
       </c>
       <c r="G21" t="inlineStr"/>
     </row>
@@ -1211,22 +1213,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1420865</v>
+        <v>1409541</v>
       </c>
       <c r="C22" t="n">
-        <v>13.6</v>
+        <v>15.5</v>
       </c>
       <c r="D22" t="n">
-        <v>-18.8</v>
+        <v>-21.9</v>
       </c>
       <c r="E22" t="n">
-        <v>25.3</v>
+        <v>25.6</v>
       </c>
       <c r="F22" t="n">
-        <v>4680</v>
+        <v>4596</v>
       </c>
       <c r="G22" t="n">
-        <v>27.3</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="23">
@@ -1236,15 +1238,15 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1070089</v>
+        <v>1085787</v>
       </c>
       <c r="C23" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>3870</v>
+        <v>4213</v>
       </c>
       <c r="G23" t="inlineStr"/>
     </row>
@@ -1255,22 +1257,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1348043</v>
+        <v>1357921</v>
       </c>
       <c r="C24" t="n">
-        <v>10.5</v>
+        <v>12.8</v>
       </c>
       <c r="D24" t="n">
-        <v>-24</v>
+        <v>-23.2</v>
       </c>
       <c r="E24" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="F24" t="n">
-        <v>5587</v>
+        <v>5649</v>
       </c>
       <c r="G24" t="n">
-        <v>27.1</v>
+        <v>26.2</v>
       </c>
     </row>
   </sheetData>
@@ -1469,7 +1471,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1495,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1507,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1519,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1543,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>

--- a/docs/exports/metrics_full.xlsx
+++ b/docs/exports/metrics_full.xlsx
@@ -475,22 +475,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>197728</v>
+        <v>194729</v>
       </c>
       <c r="C2" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="F2" t="n">
-        <v>1127</v>
+        <v>1133</v>
       </c>
       <c r="G2" t="n">
-        <v>9.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3">
@@ -500,22 +500,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79331</v>
+        <v>76898</v>
       </c>
       <c r="C3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="D3" t="n">
-        <v>-5.9</v>
+        <v>-5.3</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="F3" t="n">
-        <v>1125</v>
+        <v>1211</v>
       </c>
       <c r="G3" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="4">
@@ -525,15 +525,15 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>159044</v>
+        <v>156935</v>
       </c>
       <c r="C4" t="n">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>1260</v>
+        <v>1208</v>
       </c>
       <c r="G4" t="inlineStr"/>
     </row>
@@ -544,22 +544,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>121001</v>
+        <v>118193</v>
       </c>
       <c r="C5" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="E5" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>1066</v>
+        <v>1060</v>
       </c>
       <c r="G5" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="6">
@@ -569,22 +569,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>161635</v>
+        <v>160054</v>
       </c>
       <c r="C6" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7</v>
+        <v>-2</v>
       </c>
       <c r="E6" t="n">
-        <v>13.6</v>
+        <v>12.6</v>
       </c>
       <c r="F6" t="n">
-        <v>991</v>
+        <v>1058</v>
       </c>
       <c r="G6" t="n">
-        <v>6.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="7">
@@ -594,22 +594,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>205439</v>
+        <v>203631</v>
       </c>
       <c r="C7" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2</v>
+        <v>-0.3</v>
       </c>
       <c r="E7" t="n">
-        <v>14.4</v>
+        <v>13.6</v>
       </c>
       <c r="F7" t="n">
-        <v>1192</v>
+        <v>1250</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -619,22 +619,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>181401</v>
+        <v>180650</v>
       </c>
       <c r="C8" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5</v>
+        <v>-0.7</v>
       </c>
       <c r="E8" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="F8" t="n">
-        <v>1300</v>
+        <v>1339</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>97180</v>
+        <v>90500</v>
       </c>
       <c r="C9" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -661,15 +661,15 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>208269</v>
+        <v>208094</v>
       </c>
       <c r="C10" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>1030</v>
+        <v>1047</v>
       </c>
       <c r="G10" t="inlineStr"/>
     </row>
@@ -731,22 +731,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>740473</v>
+        <v>742447</v>
       </c>
       <c r="C2" t="n">
-        <v>8.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="D2" t="n">
-        <v>-24.3</v>
+        <v>-24.7</v>
       </c>
       <c r="E2" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="F2" t="n">
-        <v>3778</v>
+        <v>3768</v>
       </c>
       <c r="G2" t="n">
-        <v>23.4</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="3">
@@ -756,22 +756,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>823085</v>
+        <v>827104</v>
       </c>
       <c r="C3" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>-30</v>
+        <v>-29.5</v>
       </c>
       <c r="E3" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="F3" t="n">
-        <v>4446</v>
+        <v>4540</v>
       </c>
       <c r="G3" t="n">
-        <v>28.8</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="4">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1126984</v>
+        <v>1130548</v>
       </c>
       <c r="C4" t="n">
-        <v>9.5</v>
+        <v>11.3</v>
       </c>
       <c r="D4" t="n">
-        <v>-27.3</v>
+        <v>-26.7</v>
       </c>
       <c r="E4" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="F4" t="n">
-        <v>5958</v>
+        <v>5991</v>
       </c>
       <c r="G4" t="n">
         <v>27.5</v>
@@ -806,22 +806,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1042419</v>
+        <v>1054806</v>
       </c>
       <c r="C5" t="n">
-        <v>10.4</v>
+        <v>12.3</v>
       </c>
       <c r="D5" t="n">
-        <v>-28.1</v>
+        <v>-27.8</v>
       </c>
       <c r="E5" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="F5" t="n">
-        <v>5001</v>
+        <v>5099</v>
       </c>
       <c r="G5" t="n">
-        <v>26.8</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="6">
@@ -831,22 +831,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1059563</v>
+        <v>1048767</v>
       </c>
       <c r="C6" t="n">
-        <v>14.6</v>
+        <v>16.2</v>
       </c>
       <c r="D6" t="n">
-        <v>-23.1</v>
+        <v>-23.3</v>
       </c>
       <c r="E6" t="n">
-        <v>24.6</v>
+        <v>23.3</v>
       </c>
       <c r="F6" t="n">
-        <v>3592</v>
+        <v>3750</v>
       </c>
       <c r="G6" t="n">
-        <v>29.3</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="7">
@@ -856,22 +856,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1068686</v>
+        <v>1072448</v>
       </c>
       <c r="C7" t="n">
-        <v>10.4</v>
+        <v>12.3</v>
       </c>
       <c r="D7" t="n">
-        <v>-24.2</v>
+        <v>-24.7</v>
       </c>
       <c r="E7" t="n">
-        <v>22.4</v>
+        <v>21.5</v>
       </c>
       <c r="F7" t="n">
-        <v>3972</v>
+        <v>4154</v>
       </c>
       <c r="G7" t="n">
-        <v>28</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="8">
@@ -881,22 +881,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1428555</v>
+        <v>1446124</v>
       </c>
       <c r="C8" t="n">
-        <v>14.9</v>
+        <v>16.9</v>
       </c>
       <c r="D8" t="n">
-        <v>-18.2</v>
+        <v>-18.1</v>
       </c>
       <c r="E8" t="n">
-        <v>25.9</v>
+        <v>24.4</v>
       </c>
       <c r="F8" t="n">
-        <v>4590</v>
+        <v>4931</v>
       </c>
       <c r="G8" t="n">
-        <v>26</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="9">
@@ -906,22 +906,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1171546</v>
+        <v>1183444</v>
       </c>
       <c r="C9" t="n">
-        <v>10.1</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>-8.1</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>26.3</v>
+        <v>24.2</v>
       </c>
       <c r="F9" t="n">
-        <v>3715</v>
+        <v>4080</v>
       </c>
       <c r="G9" t="n">
-        <v>6.7</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="10">
@@ -931,22 +931,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2015424</v>
+        <v>2048564</v>
       </c>
       <c r="C10" t="n">
-        <v>19.5</v>
+        <v>21.6</v>
       </c>
       <c r="D10" t="n">
-        <v>-14.5</v>
+        <v>-15</v>
       </c>
       <c r="E10" t="n">
-        <v>28.3</v>
+        <v>30.3</v>
       </c>
       <c r="F10" t="n">
-        <v>5942</v>
+        <v>5626</v>
       </c>
       <c r="G10" t="n">
-        <v>28.1</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="11">
@@ -956,22 +956,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1545349</v>
+        <v>1576421</v>
       </c>
       <c r="C11" t="n">
-        <v>17.1</v>
+        <v>19.2</v>
       </c>
       <c r="D11" t="n">
-        <v>-20.1</v>
+        <v>-21.2</v>
       </c>
       <c r="E11" t="n">
-        <v>28</v>
+        <v>26.9</v>
       </c>
       <c r="F11" t="n">
-        <v>4605</v>
+        <v>4892</v>
       </c>
       <c r="G11" t="n">
-        <v>27.8</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="12">
@@ -981,22 +981,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1620022</v>
+        <v>1646701</v>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>16.6</v>
       </c>
       <c r="D12" t="n">
-        <v>-16.1</v>
+        <v>-16.5</v>
       </c>
       <c r="E12" t="n">
-        <v>29.7</v>
+        <v>27.3</v>
       </c>
       <c r="F12" t="n">
-        <v>4540</v>
+        <v>5020</v>
       </c>
       <c r="G12" t="n">
-        <v>25.1</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="13">
@@ -1006,22 +1006,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1685324</v>
+        <v>1702811</v>
       </c>
       <c r="C13" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="D13" t="n">
-        <v>-20.7</v>
+        <v>-20.3</v>
       </c>
       <c r="E13" t="n">
-        <v>27.8</v>
+        <v>26.5</v>
       </c>
       <c r="F13" t="n">
-        <v>5058</v>
+        <v>5351</v>
       </c>
       <c r="G13" t="n">
-        <v>28.1</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="14">
@@ -1031,22 +1031,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2261580</v>
+        <v>2309259</v>
       </c>
       <c r="C14" t="n">
-        <v>18.8</v>
+        <v>21.7</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.8</v>
+        <v>-14.4</v>
       </c>
       <c r="E14" t="n">
-        <v>42.4</v>
+        <v>41.2</v>
       </c>
       <c r="F14" t="n">
-        <v>4440</v>
+        <v>4672</v>
       </c>
       <c r="G14" t="n">
-        <v>21.3</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="15">
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1833048</v>
+        <v>1862908</v>
       </c>
       <c r="C15" t="n">
-        <v>17.6</v>
+        <v>20.1</v>
       </c>
       <c r="D15" t="n">
-        <v>-15.1</v>
+        <v>-14.6</v>
       </c>
       <c r="E15" t="n">
-        <v>36.7</v>
+        <v>34.6</v>
       </c>
       <c r="F15" t="n">
-        <v>4159</v>
+        <v>4486</v>
       </c>
       <c r="G15" t="n">
-        <v>23.2</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="16">
@@ -1081,22 +1081,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1717942</v>
+        <v>1740129</v>
       </c>
       <c r="C16" t="n">
-        <v>14.1</v>
+        <v>16.5</v>
       </c>
       <c r="D16" t="n">
-        <v>-15.7</v>
+        <v>-16.8</v>
       </c>
       <c r="E16" t="n">
-        <v>35.3</v>
+        <v>34.5</v>
       </c>
       <c r="F16" t="n">
-        <v>4050</v>
+        <v>4207</v>
       </c>
       <c r="G16" t="n">
-        <v>23.8</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="17">
@@ -1106,22 +1106,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2505204</v>
+        <v>2552945</v>
       </c>
       <c r="C17" t="n">
-        <v>18.9</v>
+        <v>21.2</v>
       </c>
       <c r="D17" t="n">
-        <v>-18.4</v>
+        <v>-19.6</v>
       </c>
       <c r="E17" t="n">
-        <v>39.9</v>
+        <v>39.3</v>
       </c>
       <c r="F17" t="n">
-        <v>5228</v>
+        <v>5415</v>
       </c>
       <c r="G17" t="n">
-        <v>28.6</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="18">
@@ -1131,15 +1131,15 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>947522</v>
+        <v>938112</v>
       </c>
       <c r="C18" t="n">
-        <v>7.2</v>
+        <v>9.1</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>4062</v>
+        <v>4293</v>
       </c>
       <c r="G18" t="inlineStr"/>
     </row>
@@ -1150,15 +1150,15 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2007754</v>
+        <v>2055660</v>
       </c>
       <c r="C19" t="n">
-        <v>16.7</v>
+        <v>18.6</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>6200</v>
+        <v>6083</v>
       </c>
       <c r="G19" t="inlineStr"/>
     </row>
@@ -1169,22 +1169,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1761605</v>
+        <v>1784754</v>
       </c>
       <c r="C20" t="n">
-        <v>18.6</v>
+        <v>20.6</v>
       </c>
       <c r="D20" t="n">
-        <v>-17.7</v>
+        <v>-17.4</v>
       </c>
       <c r="E20" t="n">
-        <v>30.6</v>
+        <v>29.6</v>
       </c>
       <c r="F20" t="n">
-        <v>4792</v>
+        <v>5022</v>
       </c>
       <c r="G20" t="n">
-        <v>31.5</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="21">
@@ -1194,15 +1194,15 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1380387</v>
+        <v>1403427</v>
       </c>
       <c r="C21" t="n">
-        <v>11.4</v>
+        <v>12.7</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>3260</v>
+        <v>3276</v>
       </c>
       <c r="G21" t="inlineStr"/>
     </row>
@@ -1213,22 +1213,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1409541</v>
+        <v>1409236</v>
       </c>
       <c r="C22" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>-21.9</v>
+        <v>-23</v>
       </c>
       <c r="E22" t="n">
-        <v>25.6</v>
+        <v>24.7</v>
       </c>
       <c r="F22" t="n">
-        <v>4596</v>
+        <v>4751</v>
       </c>
       <c r="G22" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="23">
@@ -1238,15 +1238,15 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1085787</v>
+        <v>1093615</v>
       </c>
       <c r="C23" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>4213</v>
+        <v>4417</v>
       </c>
       <c r="G23" t="inlineStr"/>
     </row>
@@ -1257,22 +1257,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1357921</v>
+        <v>1380642</v>
       </c>
       <c r="C24" t="n">
-        <v>12.8</v>
+        <v>14.5</v>
       </c>
       <c r="D24" t="n">
-        <v>-23.2</v>
+        <v>-22</v>
       </c>
       <c r="E24" t="n">
-        <v>20</v>
+        <v>20.4</v>
       </c>
       <c r="F24" t="n">
-        <v>5649</v>
+        <v>5627</v>
       </c>
       <c r="G24" t="n">
-        <v>26.2</v>
+        <v>25.6</v>
       </c>
     </row>
   </sheetData>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
